--- a/output/pdf_financials_xlsx/NED.xlsx
+++ b/output/pdf_financials_xlsx/NED.xlsx
@@ -1369,7 +1369,7 @@
         <v>0.029347</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.003563</v>
+        <v>-0.559123</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-1.352676</v>
@@ -1613,7 +1613,7 @@
         <v>-0.06610199999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.27778</v>
+        <v>-0.27778</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.676338</v>
@@ -1793,7 +1793,7 @@
         <v>-0.06610199999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.27778</v>
+        <v>-0.27778</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.676338</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-6.9445</v>
+        <v>6.9445</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>9.661970999999999</v>
@@ -2315,7 +2315,7 @@
         <v>-30.74626240191097</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1.266425679686362</v>
+        <v>198.7335743203136</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -6042,25 +6042,25 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.14736</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.14736</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.022437</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.022437</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.023007</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.026868</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.022437</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.192776</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0.287164</v>
@@ -12748,7 +12748,11 @@
           <t>Warrants Reserve</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -18267,7 +18271,11 @@
           <t>Share Purchase Warrants Reserve</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -31215,7 +31223,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -41209,10 +41221,10 @@
         </is>
       </c>
       <c r="G328" s="5" t="n">
-        <v>0.27778</v>
+        <v>-0.27778</v>
       </c>
       <c r="H328" s="5" t="n">
-        <v>0.676338</v>
+        <v>-0.676338</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NED.xlsx
+++ b/output/pdf_financials_xlsx/NED.xlsx
@@ -948,16 +948,16 @@
         <v>0.281343</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.346674</v>
+        <v>0.676338</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.32858</v>
+        <v>0.774632</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.162997</v>
+        <v>0.288597</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.047152</v>
+        <v>0.281609</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.022984</v>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.346674</v>
+        <v>-0.676338</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.32858</v>
+        <v>-0.774632</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.162997</v>
+        <v>-0.288597</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>-0.281609</v>
@@ -2471,52 +2471,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.054102</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.227217</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.285443</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001552</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000891</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000634</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000886</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004871</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000255</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000652</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000465</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003088</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
     </row>
     <row r="35">
@@ -2591,52 +2591,52 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.054102</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.227217</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.285443</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001552</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000891</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000634</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000886</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004871</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000255</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000652</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000465</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.003088</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
     </row>
     <row r="37">
@@ -3311,52 +3311,52 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.054102</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.227217</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.309243</v>
+        <v>0.0238</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.017802</v>
+        <v>0.01625</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000891</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000634</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.001521</v>
+        <v>0.001483</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.015446</v>
+        <v>0.006646</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.066561</v>
+        <v>0.065675</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.010405</v>
+        <v>0.005534</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.002253</v>
+        <v>0.001998</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.003487</v>
+        <v>0.002835</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.00157</v>
+        <v>0.001105</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.006168</v>
+        <v>0.00308</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.023518</v>
+        <v>0.023422</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.00428</v>
+        <v>0.004129</v>
       </c>
     </row>
     <row r="49">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">

--- a/output/pdf_financials_xlsx/NED.xlsx
+++ b/output/pdf_financials_xlsx/NED.xlsx
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.029347</v>
+        <v>-0.029347</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.559123</v>
+        <v>0.003563</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-1.352676</v>
@@ -2315,7 +2315,7 @@
         <v>-30.74626240191097</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>198.7335743203136</v>
+        <v>1.266425679686362</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -6536,34 +6536,34 @@
         <v>0.004493</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.000701</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.000185</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012249</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.010141</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.001407</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000837</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>0.00173</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001975</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.020342</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>0.019293</v>
       </c>
     </row>
     <row r="102">
@@ -23178,7 +23178,11 @@
           <t>GST Recoverable</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -29397,7 +29401,11 @@
           <t>Fair value of warrants issued pursuant to private placement</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -30621,7 +30629,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -30922,7 +30934,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -31021,7 +31037,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31930,7 +31950,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -41104,7 +41128,11 @@
           <t>DEFERRED INCOME TAX RECOVERY 8</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -42544,7 +42572,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
